--- a/salidas/empresas/EQIX.xlsx
+++ b/salidas/empresas/EQIX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>34.35151290893555</v>
+        <v>34.35152435302734</v>
       </c>
       <c r="C2" t="n">
         <v>46.93000030517578</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>38.38468933105469</v>
+        <v>38.38469314575195</v>
       </c>
       <c r="C3" t="n">
         <v>52.43999862670898</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>47.00733947753906</v>
+        <v>47.00733184814453</v>
       </c>
       <c r="C4" t="n">
         <v>64.22000122070312</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>48.23705673217773</v>
+        <v>48.23705291748047</v>
       </c>
       <c r="C5" t="n">
         <v>65.90000152587891</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>42.65942001342773</v>
+        <v>42.659423828125</v>
       </c>
       <c r="C6" t="n">
         <v>58.27999877929688</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>40.15606307983398</v>
+        <v>40.15607070922852</v>
       </c>
       <c r="C7" t="n">
         <v>54.86000061035156</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>38.34077835083008</v>
+        <v>38.34078979492188</v>
       </c>
       <c r="C8" t="n">
         <v>52.38000106811523</v>
@@ -615,7 +627,7 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>43.99160003662109</v>
+        <v>43.99160766601562</v>
       </c>
       <c r="C10" t="n">
         <v>60.09999847412109</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>50.06698989868164</v>
+        <v>50.06698226928711</v>
       </c>
       <c r="C11" t="n">
         <v>68.40000152587891</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>56.00329208374023</v>
+        <v>56.0032958984375</v>
       </c>
       <c r="C12" t="n">
         <v>76.51000213623047</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>55.35183334350586</v>
+        <v>55.35182952880859</v>
       </c>
       <c r="C13" t="n">
         <v>75.62000274658203</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>61.53703308105469</v>
+        <v>61.53702926635742</v>
       </c>
       <c r="C14" t="n">
         <v>84.06999969482422</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>60.51224899291992</v>
+        <v>60.51224136352539</v>
       </c>
       <c r="C15" t="n">
         <v>82.66999816894531</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>62.67888259887695</v>
+        <v>62.67890167236328</v>
       </c>
       <c r="C16" t="n">
         <v>85.62999725341797</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>61.09782791137695</v>
+        <v>61.09783554077148</v>
       </c>
       <c r="C17" t="n">
         <v>83.47000122070312</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>63.95985794067383</v>
+        <v>63.95985412597656</v>
       </c>
       <c r="C18" t="n">
         <v>87.37999725341797</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>66.95359802246094</v>
+        <v>66.95363616943359</v>
       </c>
       <c r="C19" t="n">
         <v>91.47000122070312</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>63.61581039428711</v>
+        <v>63.61582183837891</v>
       </c>
       <c r="C20" t="n">
         <v>86.91000366210938</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>64.78699493408203</v>
+        <v>64.78696441650391</v>
       </c>
       <c r="C21" t="n">
         <v>88.51000213623047</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>64.91874694824219</v>
+        <v>64.91873168945312</v>
       </c>
       <c r="C22" t="n">
         <v>88.69000244140625</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>85.39202880859375</v>
+        <v>85.39203643798828</v>
       </c>
       <c r="C23" t="n">
         <v>116.6600036621094</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>76.20574951171875</v>
+        <v>76.20577239990234</v>
       </c>
       <c r="C24" t="n">
         <v>104.1100006103516</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>73.98056793212891</v>
+        <v>73.98058319091797</v>
       </c>
       <c r="C25" t="n">
         <v>101.0699996948242</v>
@@ -938,7 +950,7 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>50.76237487792969</v>
+        <v>50.76236724853516</v>
       </c>
       <c r="C27" t="n">
         <v>69.34999847412109</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>48.66891098022461</v>
+        <v>48.66893768310547</v>
       </c>
       <c r="C28" t="n">
         <v>66.48999786376953</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>66.18502807617188</v>
+        <v>66.18503570556641</v>
       </c>
       <c r="C29" t="n">
         <v>90.41999816894531</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>69.89615631103516</v>
+        <v>69.89617156982422</v>
       </c>
       <c r="C30" t="n">
         <v>95.48999786376953</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>65.30667877197266</v>
+        <v>65.30669403076172</v>
       </c>
       <c r="C31" t="n">
         <v>89.22000122070312</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>59.55337524414062</v>
+        <v>59.55335998535156</v>
       </c>
       <c r="C32" t="n">
         <v>81.36000061035156</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>58.92386245727539</v>
+        <v>58.92388153076172</v>
       </c>
       <c r="C33" t="n">
         <v>80.5</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>50.84286880493164</v>
+        <v>50.84289169311523</v>
       </c>
       <c r="C34" t="n">
         <v>69.45999908447266</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>45.68979263305664</v>
+        <v>45.68979644775391</v>
       </c>
       <c r="C35" t="n">
         <v>62.41999816894531</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>33.23891448974609</v>
+        <v>33.23892593383789</v>
       </c>
       <c r="C36" t="n">
         <v>45.40999984741211</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>38.93366241455078</v>
+        <v>38.93367767333984</v>
       </c>
       <c r="C37" t="n">
         <v>53.18999862670898</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>39.05078506469727</v>
+        <v>39.05078887939453</v>
       </c>
       <c r="C38" t="n">
         <v>53.34999847412109</v>
@@ -1185,7 +1197,7 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>41.10031509399414</v>
+        <v>41.10031890869141</v>
       </c>
       <c r="C40" t="n">
         <v>56.15000152587891</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>51.40651702880859</v>
+        <v>51.4065055847168</v>
       </c>
       <c r="C41" t="n">
         <v>70.23000335693359</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>54.45882034301758</v>
+        <v>54.45883560180664</v>
       </c>
       <c r="C42" t="n">
         <v>74.40000152587891</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>53.24375915527344</v>
+        <v>53.24375152587891</v>
       </c>
       <c r="C43" t="n">
         <v>72.73999786376953</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>59.82421112060547</v>
+        <v>59.82419204711914</v>
       </c>
       <c r="C44" t="n">
         <v>81.73000335693359</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>61.75662231445312</v>
+        <v>61.75661087036133</v>
       </c>
       <c r="C45" t="n">
         <v>84.37000274658203</v>
@@ -1318,7 +1330,7 @@
       <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
@@ -1337,11 +1349,11 @@
       <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>62.45196914672852</v>
+        <v>62.45199203491211</v>
       </c>
       <c r="C47" t="n">
         <v>85.31999969482422</v>
@@ -1356,7 +1368,7 @@
       <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
@@ -1375,11 +1387,11 @@
       <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>77.69899749755859</v>
+        <v>77.69900512695312</v>
       </c>
       <c r="C49" t="n">
         <v>106.1500015258789</v>
@@ -1394,11 +1406,11 @@
       <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>70.43780517578125</v>
+        <v>70.43782806396484</v>
       </c>
       <c r="C50" t="n">
         <v>96.23000335693359</v>
@@ -1413,11 +1425,11 @@
       <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>69.1495361328125</v>
+        <v>69.14952087402344</v>
       </c>
       <c r="C51" t="n">
         <v>94.47000122070312</v>
@@ -1432,11 +1444,11 @@
       <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>71.25029754638672</v>
+        <v>71.25030517578125</v>
       </c>
       <c r="C52" t="n">
         <v>97.33999633789062</v>
@@ -1451,11 +1463,11 @@
       <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>73.67314147949219</v>
+        <v>73.67312622070312</v>
       </c>
       <c r="C53" t="n">
         <v>100.6500015258789</v>
@@ -1470,11 +1482,11 @@
       <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>67.348876953125</v>
+        <v>67.34889984130859</v>
       </c>
       <c r="C54" t="n">
         <v>92.01000213623047</v>
@@ -1489,11 +1501,11 @@
       <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>59.45090103149414</v>
+        <v>59.45087814331055</v>
       </c>
       <c r="C55" t="n">
         <v>81.22000122070312</v>
@@ -1508,11 +1520,11 @@
       <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>68.44682312011719</v>
+        <v>68.44685363769531</v>
       </c>
       <c r="C56" t="n">
         <v>93.51000213623047</v>
@@ -1527,11 +1539,11 @@
       <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>66.76332092285156</v>
+        <v>66.76332855224609</v>
       </c>
       <c r="C57" t="n">
         <v>91.20999908447266</v>
@@ -1552,7 +1564,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
@@ -1577,11 +1589,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>61.66143035888672</v>
+        <v>61.66144943237305</v>
       </c>
       <c r="C59" t="n">
         <v>84.23999786376953</v>
@@ -1602,11 +1614,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>56.80114364624023</v>
+        <v>56.80112457275391</v>
       </c>
       <c r="C60" t="n">
         <v>77.59999847412109</v>
@@ -1627,11 +1639,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>59.48018646240234</v>
+        <v>59.48017501831055</v>
       </c>
       <c r="C61" t="n">
         <v>81.26000213623047</v>
@@ -1652,7 +1664,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
@@ -1677,11 +1689,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>63.27182769775391</v>
+        <v>63.27177810668945</v>
       </c>
       <c r="C63" t="n">
         <v>86.44000244140625</v>
@@ -1702,11 +1714,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>66.68279266357422</v>
+        <v>66.68277740478516</v>
       </c>
       <c r="C64" t="n">
         <v>91.09999847412109</v>
@@ -1727,11 +1739,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>73.68045043945312</v>
+        <v>73.68044281005859</v>
       </c>
       <c r="C65" t="n">
         <v>100.6600036621094</v>
@@ -1752,7 +1764,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
@@ -1777,11 +1789,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>73.94398498535156</v>
+        <v>73.94396209716797</v>
       </c>
       <c r="C67" t="n">
         <v>101.0199966430664</v>
@@ -1802,11 +1814,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>76.46929931640625</v>
+        <v>76.46926116943359</v>
       </c>
       <c r="C68" t="n">
         <v>104.4700012207031</v>
@@ -1827,11 +1839,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>68.83479309082031</v>
+        <v>68.83477783203125</v>
       </c>
       <c r="C69" t="n">
         <v>94.04000091552734</v>
@@ -1852,11 +1864,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>65.02120971679688</v>
+        <v>65.02121734619141</v>
       </c>
       <c r="C70" t="n">
         <v>88.83000183105469</v>
@@ -1877,11 +1889,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>70.2767333984375</v>
+        <v>70.27677917480469</v>
       </c>
       <c r="C71" t="n">
         <v>96.01000213623047</v>
@@ -1902,11 +1914,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>73.21199798583984</v>
+        <v>73.21199035644531</v>
       </c>
       <c r="C72" t="n">
         <v>100.0199966430664</v>
@@ -1927,7 +1939,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
@@ -1952,11 +1964,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>87.80754089355469</v>
+        <v>87.80754852294922</v>
       </c>
       <c r="C74" t="n">
         <v>119.9599990844727</v>
@@ -1977,11 +1989,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>102.6080551147461</v>
+        <v>102.608039855957</v>
       </c>
       <c r="C75" t="n">
         <v>140.1799926757812</v>
@@ -2006,11 +2018,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>115.2492370605469</v>
+        <v>115.2491912841797</v>
       </c>
       <c r="C76" t="n">
         <v>157.4499969482422</v>
@@ -2035,11 +2047,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>120.1900177001953</v>
+        <v>120.1900405883789</v>
       </c>
       <c r="C77" t="n">
         <v>164.1999969482422</v>
@@ -2064,7 +2076,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
@@ -2093,11 +2105,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>128.5711364746094</v>
+        <v>128.5711059570312</v>
       </c>
       <c r="C79" t="n">
         <v>175.6499938964844</v>
@@ -2122,11 +2134,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>130.4229736328125</v>
+        <v>130.4230041503906</v>
       </c>
       <c r="C80" t="n">
         <v>178.1799926757812</v>
@@ -2151,11 +2163,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>144.6745910644531</v>
+        <v>144.6746215820312</v>
       </c>
       <c r="C81" t="n">
         <v>197.6499938964844</v>
@@ -2180,11 +2192,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>150.8231353759766</v>
+        <v>150.8231201171875</v>
       </c>
       <c r="C82" t="n">
         <v>206.0500030517578</v>
@@ -2209,11 +2221,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>132.1871032714844</v>
+        <v>132.1871337890625</v>
       </c>
       <c r="C83" t="n">
         <v>180.5899963378906</v>
@@ -2238,11 +2250,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>135.9714050292969</v>
+        <v>135.9713897705078</v>
       </c>
       <c r="C84" t="n">
         <v>185.7599945068359</v>
@@ -2267,11 +2279,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>150.9329376220703</v>
+        <v>150.9329223632812</v>
       </c>
       <c r="C85" t="n">
         <v>206.1999969482422</v>
@@ -2296,11 +2308,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>157.6891021728516</v>
+        <v>157.6890869140625</v>
       </c>
       <c r="C86" t="n">
         <v>215.4299926757812</v>
@@ -2325,11 +2337,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>154.8489990234375</v>
+        <v>154.8489685058594</v>
       </c>
       <c r="C87" t="n">
         <v>211.5500030517578</v>
@@ -2354,11 +2366,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>158.3332061767578</v>
+        <v>158.3332214355469</v>
       </c>
       <c r="C88" t="n">
         <v>216.3099975585938</v>
@@ -2383,11 +2395,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>156.7155609130859</v>
+        <v>156.7155151367188</v>
       </c>
       <c r="C89" t="n">
         <v>214.1000061035156</v>
@@ -2412,11 +2424,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>148.3271179199219</v>
+        <v>148.3271331787109</v>
       </c>
       <c r="C90" t="n">
         <v>202.6399993896484</v>
@@ -2441,11 +2453,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>135.2101440429688</v>
+        <v>135.2101745605469</v>
       </c>
       <c r="C91" t="n">
         <v>184.7200012207031</v>
@@ -2470,11 +2482,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>131.2794494628906</v>
+        <v>131.2794952392578</v>
       </c>
       <c r="C92" t="n">
         <v>179.3500061035156</v>
@@ -2499,11 +2511,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>127.173095703125</v>
+        <v>127.1731033325195</v>
       </c>
       <c r="C93" t="n">
         <v>173.7400054931641</v>
@@ -2528,11 +2540,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>134.4269561767578</v>
+        <v>134.4269714355469</v>
       </c>
       <c r="C94" t="n">
         <v>183.6499938964844</v>
@@ -2557,7 +2569,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
@@ -2586,11 +2598,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>117.6281585693359</v>
+        <v>117.6281890869141</v>
       </c>
       <c r="C96" t="n">
         <v>160.6999969482422</v>
@@ -2615,11 +2627,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>129.8887176513672</v>
+        <v>129.888671875</v>
       </c>
       <c r="C97" t="n">
         <v>177.4499969482422</v>
@@ -2644,11 +2656,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>135.5615386962891</v>
+        <v>135.5615234375</v>
       </c>
       <c r="C98" t="n">
         <v>185.1999969482422</v>
@@ -2673,11 +2685,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>139.0456695556641</v>
+        <v>139.0457458496094</v>
       </c>
       <c r="C99" t="n">
         <v>189.9600067138672</v>
@@ -2702,11 +2714,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>135.2979888916016</v>
+        <v>135.2979583740234</v>
       </c>
       <c r="C100" t="n">
         <v>184.8399963378906</v>
@@ -2731,11 +2743,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>137.4719848632812</v>
+        <v>137.4719696044922</v>
       </c>
       <c r="C101" t="n">
         <v>187.8099975585938</v>
@@ -2760,11 +2772,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>145.4796905517578</v>
+        <v>145.4797515869141</v>
       </c>
       <c r="C102" t="n">
         <v>198.75</v>
@@ -2789,7 +2801,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
@@ -2818,7 +2830,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
@@ -2847,11 +2859,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>159.7605438232422</v>
+        <v>159.7605590820312</v>
       </c>
       <c r="C105" t="n">
         <v>218.2599945068359</v>
@@ -2876,11 +2888,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>155.5297546386719</v>
+        <v>155.5297698974609</v>
       </c>
       <c r="C106" t="n">
         <v>212.4799957275391</v>
@@ -2905,11 +2917,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>158.9102325439453</v>
+        <v>158.9101867675781</v>
       </c>
       <c r="C107" t="n">
         <v>208.8999938964844</v>
@@ -2934,7 +2946,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
@@ -2963,11 +2975,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>172.4734802246094</v>
+        <v>172.4734954833984</v>
       </c>
       <c r="C109" t="n">
         <v>226.7299957275391</v>
@@ -2992,11 +3004,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>164.9654083251953</v>
+        <v>164.9653778076172</v>
       </c>
       <c r="C110" t="n">
         <v>216.8600006103516</v>
@@ -3021,11 +3033,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>170.5336761474609</v>
+        <v>170.5337219238281</v>
       </c>
       <c r="C111" t="n">
         <v>224.1799926757812</v>
@@ -3050,11 +3062,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>178.4092407226562</v>
+        <v>178.4091949462891</v>
       </c>
       <c r="C112" t="n">
         <v>232.8500061035156</v>
@@ -3077,11 +3089,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>196.0930328369141</v>
+        <v>196.093017578125</v>
       </c>
       <c r="C113" t="n">
         <v>255.9299926757812</v>
@@ -3104,11 +3116,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>206.6970520019531</v>
+        <v>206.6970062255859</v>
       </c>
       <c r="C114" t="n">
         <v>268.0700073242188</v>
@@ -3131,11 +3143,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>195.8482818603516</v>
+        <v>195.8482971191406</v>
       </c>
       <c r="C115" t="n">
         <v>254</v>
@@ -3158,11 +3170,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>215.0552978515625</v>
+        <v>215.0552825927734</v>
       </c>
       <c r="C116" t="n">
         <v>278.9100036621094</v>
@@ -3185,11 +3197,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>209.3117370605469</v>
+        <v>209.3115997314453</v>
       </c>
       <c r="C117" t="n">
         <v>269.7699890136719</v>
@@ -3212,11 +3224,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>212.1280517578125</v>
+        <v>212.1281433105469</v>
       </c>
       <c r="C118" t="n">
         <v>273.3999938964844</v>
@@ -3239,11 +3251,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>239.4410247802734</v>
+        <v>239.4410858154297</v>
       </c>
       <c r="C119" t="n">
         <v>296.6799926757812</v>
@@ -3266,11 +3278,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>239.2957305908203</v>
+        <v>239.2957916259766</v>
       </c>
       <c r="C120" t="n">
         <v>296.5</v>
@@ -3293,11 +3305,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>245.4345550537109</v>
+        <v>245.4346313476562</v>
       </c>
       <c r="C121" t="n">
         <v>302.3999938964844</v>
@@ -3320,11 +3332,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>252.0655517578125</v>
+        <v>252.0654296875</v>
       </c>
       <c r="C122" t="n">
         <v>310.5700073242188</v>
@@ -3347,11 +3359,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>246.4816131591797</v>
+        <v>246.4815063476562</v>
       </c>
       <c r="C123" t="n">
         <v>303.6900024414062</v>
@@ -3376,11 +3388,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>269.936767578125</v>
+        <v>269.9367370605469</v>
       </c>
       <c r="C124" t="n">
         <v>330.7099914550781</v>
@@ -3405,11 +3417,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>269.6428833007812</v>
+        <v>269.64306640625</v>
       </c>
       <c r="C125" t="n">
         <v>330.3500061035156</v>
@@ -3434,11 +3446,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>296.9831848144531</v>
+        <v>296.9832763671875</v>
       </c>
       <c r="C126" t="n">
         <v>362</v>
@@ -3463,11 +3475,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>318.0919799804688</v>
+        <v>318.0919494628906</v>
       </c>
       <c r="C127" t="n">
         <v>387.7300109863281</v>
@@ -3492,11 +3504,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>305.9008483886719</v>
+        <v>305.9007873535156</v>
       </c>
       <c r="C128" t="n">
         <v>372.8699951171875</v>
@@ -3521,11 +3533,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>303.8906555175781</v>
+        <v>303.8905944824219</v>
       </c>
       <c r="C129" t="n">
         <v>368.6499938964844</v>
@@ -3550,11 +3562,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>296.9662475585938</v>
+        <v>296.9662780761719</v>
       </c>
       <c r="C130" t="n">
         <v>360.25</v>
@@ -3579,7 +3591,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
@@ -3608,11 +3620,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>280.762939453125</v>
+        <v>280.7628479003906</v>
       </c>
       <c r="C132" t="n">
         <v>338.760009765625</v>
@@ -3637,7 +3649,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
@@ -3666,11 +3678,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>319.0698547363281</v>
+        <v>319.0698852539062</v>
       </c>
       <c r="C134" t="n">
         <v>384.9800109863281</v>
@@ -3695,11 +3707,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>313.3641357421875</v>
+        <v>313.3641052246094</v>
       </c>
       <c r="C135" t="n">
         <v>376.0700073242188</v>
@@ -3724,11 +3736,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>333.6122131347656</v>
+        <v>333.6122741699219</v>
       </c>
       <c r="C136" t="n">
         <v>400.3699951171875</v>
@@ -3753,11 +3765,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>348.0527038574219</v>
+        <v>348.0526733398438</v>
       </c>
       <c r="C137" t="n">
         <v>417.7000122070312</v>
@@ -3782,11 +3794,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>369.206298828125</v>
+        <v>369.2063293457031</v>
       </c>
       <c r="C138" t="n">
         <v>441.010009765625</v>
@@ -3811,11 +3823,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>359.2857666015625</v>
+        <v>359.2857055664062</v>
       </c>
       <c r="C139" t="n">
         <v>429.1600036621094</v>
@@ -3840,11 +3852,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>377.3436889648438</v>
+        <v>377.3437805175781</v>
       </c>
       <c r="C140" t="n">
         <v>450.7300109863281</v>
@@ -3869,11 +3881,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>393.895751953125</v>
+        <v>393.8957214355469</v>
       </c>
       <c r="C141" t="n">
         <v>468.4100036621094</v>
@@ -3898,11 +3910,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>375.3030090332031</v>
+        <v>375.302978515625</v>
       </c>
       <c r="C142" t="n">
         <v>446.2999877929688</v>
@@ -3927,11 +3939,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>389.766845703125</v>
+        <v>389.7669067382812</v>
       </c>
       <c r="C143" t="n">
         <v>463.5</v>
@@ -3956,11 +3968,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>392.2198181152344</v>
+        <v>392.2197265625</v>
       </c>
       <c r="C144" t="n">
         <v>464.489990234375</v>
@@ -3985,11 +3997,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>382.7031860351562</v>
+        <v>382.7032165527344</v>
       </c>
       <c r="C145" t="n">
         <v>453.2200012207031</v>
@@ -4014,11 +4026,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>384.3666381835938</v>
+        <v>384.3667602539062</v>
       </c>
       <c r="C146" t="n">
         <v>455.1900024414062</v>
@@ -4043,11 +4055,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>333.0376892089844</v>
+        <v>333.0376586914062</v>
       </c>
       <c r="C147" t="n">
         <v>392.1000061035156</v>
@@ -4072,11 +4084,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>355.1552429199219</v>
+        <v>355.1552124023438</v>
       </c>
       <c r="C148" t="n">
         <v>418.1400146484375</v>
@@ -4101,11 +4113,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>357.406005859375</v>
+        <v>357.4060668945312</v>
       </c>
       <c r="C149" t="n">
         <v>420.7900085449219</v>
@@ -4130,11 +4142,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>339.0607604980469</v>
+        <v>339.0606689453125</v>
       </c>
       <c r="C150" t="n">
         <v>396.8500061035156</v>
@@ -4159,11 +4171,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>367.2894287109375</v>
+        <v>367.2894592285156</v>
       </c>
       <c r="C151" t="n">
         <v>429.8900146484375</v>
@@ -4188,11 +4200,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>375.3120422363281</v>
+        <v>375.3121032714844</v>
       </c>
       <c r="C152" t="n">
         <v>439.2799987792969</v>
@@ -4217,7 +4229,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
@@ -4246,11 +4258,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>371.7864685058594</v>
+        <v>371.7864990234375</v>
       </c>
       <c r="C154" t="n">
         <v>432.8900146484375</v>
@@ -4275,11 +4287,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>325.27978515625</v>
+        <v>325.2798461914062</v>
       </c>
       <c r="C155" t="n">
         <v>378.739990234375</v>
@@ -4304,11 +4316,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>332.8455200195312</v>
+        <v>332.8454284667969</v>
       </c>
       <c r="C156" t="n">
         <v>385.2799987792969</v>
@@ -4333,7 +4345,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
@@ -4362,11 +4374,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>340.3787231445312</v>
+        <v>340.3787841796875</v>
       </c>
       <c r="C158" t="n">
         <v>394</v>
@@ -4391,11 +4403,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>367.9741821289062</v>
+        <v>367.9740905761719</v>
       </c>
       <c r="C159" t="n">
         <v>423.5</v>
@@ -4420,11 +4432,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>393.7453002929688</v>
+        <v>393.745361328125</v>
       </c>
       <c r="C160" t="n">
         <v>453.1600036621094</v>
@@ -4449,11 +4461,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>395.0835266113281</v>
+        <v>395.0834655761719</v>
       </c>
       <c r="C161" t="n">
         <v>454.7000122070312</v>
@@ -4478,11 +4490,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>424.2710876464844</v>
+        <v>424.2709655761719</v>
       </c>
       <c r="C162" t="n">
         <v>485.7900085449219</v>
@@ -4507,11 +4519,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>440.4282836914062</v>
+        <v>440.42822265625</v>
       </c>
       <c r="C163" t="n">
         <v>504.2900085449219</v>
@@ -4536,11 +4548,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>438.5155944824219</v>
+        <v>438.515625</v>
       </c>
       <c r="C164" t="n">
         <v>502.1000061035156</v>
@@ -4565,11 +4577,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>487.9945373535156</v>
+        <v>487.9945983886719</v>
       </c>
       <c r="C165" t="n">
         <v>556.280029296875</v>
@@ -4594,11 +4606,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>505.9956359863281</v>
+        <v>505.9954833984375</v>
       </c>
       <c r="C166" t="n">
         <v>576.7999877929688</v>
@@ -4623,11 +4635,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>497.20556640625</v>
+        <v>497.2057495117188</v>
       </c>
       <c r="C167" t="n">
         <v>566.780029296875</v>
@@ -4652,11 +4664,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>499.4680786132812</v>
+        <v>499.4681091308594</v>
       </c>
       <c r="C168" t="n">
         <v>566.8499755859375</v>
@@ -4681,7 +4693,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
@@ -4710,11 +4722,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>519.62841796875</v>
+        <v>519.6282958984375</v>
       </c>
       <c r="C170" t="n">
         <v>589.72998046875</v>
@@ -4739,11 +4751,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>506.8011779785156</v>
+        <v>506.8013305664062</v>
       </c>
       <c r="C171" t="n">
         <v>572.7999877929688</v>
@@ -4768,11 +4780,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>552.6062622070312</v>
+        <v>552.6065063476562</v>
       </c>
       <c r="C172" t="n">
         <v>624.5700073242188</v>
@@ -4797,7 +4809,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
@@ -4826,11 +4838,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>619.7369384765625</v>
+        <v>619.73681640625</v>
       </c>
       <c r="C174" t="n">
         <v>697.6300048828125</v>
@@ -4855,11 +4867,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>623.8855590820312</v>
+        <v>623.8854370117188</v>
       </c>
       <c r="C175" t="n">
         <v>702.2999877929688</v>
@@ -4884,7 +4896,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
@@ -4913,7 +4925,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
@@ -4942,11 +4954,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>677.593017578125</v>
+        <v>677.5931396484375</v>
       </c>
       <c r="C178" t="n">
         <v>760.1300048828125</v>
@@ -4971,11 +4983,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>651.83984375</v>
+        <v>651.8399658203125</v>
       </c>
       <c r="C179" t="n">
         <v>731.239990234375</v>
@@ -5000,11 +5012,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>624.2210693359375</v>
+        <v>624.2210083007812</v>
       </c>
       <c r="C180" t="n">
         <v>697.7899780273438</v>
@@ -5029,7 +5041,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
@@ -5058,11 +5070,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>661.9449462890625</v>
+        <v>661.9451904296875</v>
       </c>
       <c r="C182" t="n">
         <v>739.9600219726562</v>
@@ -5087,7 +5099,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
@@ -5116,7 +5128,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
@@ -5145,11 +5157,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>647.5543212890625</v>
+        <v>647.5540771484375</v>
       </c>
       <c r="C185" t="n">
         <v>720.760009765625</v>
@@ -5174,11 +5186,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>664.5606079101562</v>
+        <v>664.5604858398438</v>
       </c>
       <c r="C186" t="n">
         <v>736.719970703125</v>
@@ -5203,11 +5215,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>723.9878540039062</v>
+        <v>723.9879150390625</v>
       </c>
       <c r="C187" t="n">
         <v>802.5999755859375</v>
@@ -5232,11 +5244,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>740.053466796875</v>
+        <v>740.0535888671875</v>
       </c>
       <c r="C188" t="n">
         <v>820.4099731445312</v>
@@ -5261,11 +5273,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>763.49951171875</v>
+        <v>763.4993896484375</v>
       </c>
       <c r="C189" t="n">
         <v>843.4500122070312</v>
@@ -5290,7 +5302,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
@@ -5319,11 +5331,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>757.7242431640625</v>
+        <v>757.7241821289062</v>
       </c>
       <c r="C191" t="n">
         <v>837.0700073242188</v>
@@ -5348,11 +5360,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>737.8658447265625</v>
+        <v>737.8659057617188</v>
       </c>
       <c r="C192" t="n">
         <v>812.2000122070312</v>
@@ -5377,11 +5389,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>768.42724609375</v>
+        <v>768.427001953125</v>
       </c>
       <c r="C193" t="n">
         <v>845.8400268554688</v>
@@ -5406,11 +5418,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>658.5558471679688</v>
+        <v>658.5557861328125</v>
       </c>
       <c r="C194" t="n">
         <v>724.9000244140625</v>
@@ -5435,11 +5447,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>644.774169921875</v>
+        <v>644.7740478515625</v>
       </c>
       <c r="C195" t="n">
         <v>709.72998046875</v>
@@ -5464,11 +5476,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>676.6555786132812</v>
+        <v>676.6556396484375</v>
       </c>
       <c r="C196" t="n">
         <v>741.6199951171875</v>
@@ -5493,11 +5505,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>656.0900268554688</v>
+        <v>656.0901489257812</v>
       </c>
       <c r="C197" t="n">
         <v>719.0800170898438</v>
@@ -5522,11 +5534,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>629.9232788085938</v>
+        <v>629.9232177734375</v>
       </c>
       <c r="C198" t="n">
         <v>687.0900268554688</v>
@@ -5551,7 +5563,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
@@ -5580,11 +5592,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>645.1878051757812</v>
+        <v>645.1879272460938</v>
       </c>
       <c r="C200" t="n">
         <v>703.739990234375</v>
@@ -5609,11 +5621,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>605.3010864257812</v>
+        <v>605.3009643554688</v>
       </c>
       <c r="C201" t="n">
         <v>657.3699951171875</v>
@@ -5638,11 +5650,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>523.7833862304688</v>
+        <v>523.783447265625</v>
       </c>
       <c r="C202" t="n">
         <v>568.8400268554688</v>
@@ -5667,7 +5679,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
@@ -5696,11 +5708,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>639.045654296875</v>
+        <v>639.0455932617188</v>
       </c>
       <c r="C204" t="n">
         <v>690.6500244140625</v>
@@ -5725,11 +5737,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>606.0869750976562</v>
+        <v>606.0870361328125</v>
       </c>
       <c r="C205" t="n">
         <v>655.030029296875</v>
@@ -5754,11 +5766,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>682.9778442382812</v>
+        <v>682.9779052734375</v>
       </c>
       <c r="C206" t="n">
         <v>738.1300048828125</v>
@@ -5783,11 +5795,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>636.8434448242188</v>
+        <v>636.843505859375</v>
       </c>
       <c r="C207" t="n">
         <v>688.27001953125</v>
@@ -5812,11 +5824,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>670.405517578125</v>
+        <v>670.4056396484375</v>
       </c>
       <c r="C208" t="n">
         <v>721.0399780273438</v>
@@ -5841,11 +5853,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>673.2322387695312</v>
+        <v>673.232177734375</v>
       </c>
       <c r="C209" t="n">
         <v>724.0800170898438</v>
@@ -5870,11 +5882,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>696.46240234375</v>
+        <v>696.4625854492188</v>
       </c>
       <c r="C210" t="n">
         <v>745.5499877929688</v>
@@ -5899,11 +5911,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>732.3247680664062</v>
+        <v>732.3248291015625</v>
       </c>
       <c r="C211" t="n">
         <v>783.9400024414062</v>
@@ -5928,11 +5940,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>756.5941772460938</v>
+        <v>756.59423828125</v>
       </c>
       <c r="C212" t="n">
         <v>809.9199829101562</v>
@@ -5957,11 +5969,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>733.2864379882812</v>
+        <v>733.286376953125</v>
       </c>
       <c r="C213" t="n">
         <v>781.3800048828125</v>
@@ -5986,11 +5998,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>681.5591430664062</v>
+        <v>681.55908203125</v>
       </c>
       <c r="C214" t="n">
         <v>726.260009765625</v>
@@ -6015,11 +6027,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>684.73095703125</v>
+        <v>684.7310791015625</v>
       </c>
       <c r="C215" t="n">
         <v>729.6400146484375</v>
@@ -6044,11 +6056,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>769.1434326171875</v>
+        <v>769.1433715820312</v>
       </c>
       <c r="C216" t="n">
         <v>815.010009765625</v>
@@ -6073,7 +6085,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -6102,7 +6114,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
@@ -6131,11 +6143,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>842.8910522460938</v>
+        <v>842.8909912109375</v>
       </c>
       <c r="C219" t="n">
         <v>888.8200073242188</v>
@@ -6160,11 +6172,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>782.6818237304688</v>
+        <v>782.6817016601562</v>
       </c>
       <c r="C220" t="n">
         <v>825.3300170898438</v>
@@ -6189,7 +6201,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
@@ -6218,11 +6230,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>727.4502563476562</v>
+        <v>727.4503173828125</v>
       </c>
       <c r="C222" t="n">
         <v>762.97998046875</v>
@@ -6247,11 +6259,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>721.3674926757812</v>
+        <v>721.3673706054688</v>
       </c>
       <c r="C223" t="n">
         <v>756.5999755859375</v>
@@ -6276,11 +6288,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>753.4409790039062</v>
+        <v>753.44091796875</v>
       </c>
       <c r="C224" t="n">
         <v>790.239990234375</v>
@@ -6305,7 +6317,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
@@ -6334,11 +6346,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>850.66259765625</v>
+        <v>850.6626586914062</v>
       </c>
       <c r="C226" t="n">
         <v>887.6300048828125</v>
@@ -6363,7 +6375,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6392,11 +6404,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>945.0624389648438</v>
+        <v>945.0623779296875</v>
       </c>
       <c r="C228" t="n">
         <v>981.47998046875</v>
@@ -6421,11 +6433,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>907.9041748046875</v>
+        <v>907.904296875</v>
       </c>
       <c r="C229" t="n">
         <v>942.8900146484375</v>
@@ -6450,11 +6462,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>879.7589111328125</v>
+        <v>879.7587890625</v>
       </c>
       <c r="C230" t="n">
         <v>913.6599731445312</v>
@@ -6479,11 +6491,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>875.58349609375</v>
+        <v>875.5835571289062</v>
       </c>
       <c r="C231" t="n">
         <v>904.6199951171875</v>
@@ -6508,11 +6520,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>789.1787719726562</v>
+        <v>789.1788330078125</v>
       </c>
       <c r="C232" t="n">
         <v>815.3499755859375</v>
@@ -6537,7 +6549,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6566,7 +6578,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6595,11 +6607,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>774.081787109375</v>
+        <v>774.0818481445312</v>
       </c>
       <c r="C235" t="n">
         <v>795.469970703125</v>
@@ -6624,7 +6636,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6653,11 +6665,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>769.7186279296875</v>
+        <v>769.7186889648438</v>
       </c>
       <c r="C237" t="n">
         <v>786.1900024414062</v>
@@ -6682,7 +6694,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6711,7 +6723,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6740,7 +6752,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6769,11 +6781,11 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>754.6507568359375</v>
+        <v>754.6506958007812</v>
       </c>
       <c r="C241" t="n">
         <v>766.1599731445312</v>
@@ -6798,11 +6810,11 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>808.5979614257812</v>
+        <v>808.5980224609375</v>
       </c>
       <c r="C242" t="n">
         <v>820.9299926757812</v>
@@ -6827,7 +6839,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6856,7 +6868,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -6885,7 +6897,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -6914,7 +6926,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -6943,7 +6955,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -6972,7 +6984,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7001,7 +7013,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7030,32 +7042,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>1037.660034179688</v>
+        <v>1034.760009765625</v>
       </c>
       <c r="C250" t="n">
-        <v>1037.660034179688</v>
+        <v>1034.760009765625</v>
       </c>
       <c r="D250" t="n">
-        <v>8159600</v>
+        <v>8556700</v>
       </c>
       <c r="E250" t="n">
         <v>15.54</v>
       </c>
       <c r="F250" t="n">
-        <v>66.77348997295287</v>
+        <v>66.58687321529119</v>
       </c>
       <c r="G250" t="n">
         <v>98671686</v>
       </c>
       <c r="H250" t="n">
-        <v>102387665067.3274</v>
+        <v>102101514768.9507</v>
       </c>
       <c r="I250" t="n">
-        <v>0.08269444184829274</v>
+        <v>0.0867188992797792</v>
       </c>
     </row>
   </sheetData>
@@ -7087,75 +7099,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40394</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7191,13 +7203,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40480</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7233,13 +7245,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40662</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7275,13 +7287,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40394</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7317,13 +7329,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40480</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7359,13 +7371,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40662</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7401,13 +7413,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40753</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7443,13 +7455,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40844</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7485,13 +7497,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7518,7 +7530,7 @@
       <c r="I10" t="n">
         <v>1.72</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="K10" t="n">
@@ -7531,13 +7543,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>41026</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7564,7 +7576,7 @@
       <c r="I11" t="n">
         <v>1.9</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>41026</v>
       </c>
       <c r="K11" t="n">
@@ -7577,13 +7589,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>41117</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7610,7 +7622,7 @@
       <c r="I12" t="n">
         <v>1.99</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>41117</v>
       </c>
       <c r="K12" t="n">
@@ -7623,13 +7635,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>41219</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7656,7 +7668,7 @@
       <c r="I13" t="n">
         <v>2.37</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>41219</v>
       </c>
       <c r="K13" t="n">
@@ -7669,13 +7681,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>41331</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7702,7 +7714,7 @@
       <c r="I14" t="n">
         <v>2.899999999999999</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>41331</v>
       </c>
       <c r="K14" t="n">
@@ -7715,13 +7727,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41390</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7748,7 +7760,7 @@
       <c r="I15" t="n">
         <v>2.899999999999999</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41390</v>
       </c>
       <c r="K15" t="n">
@@ -7761,13 +7773,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41481</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7794,7 +7806,7 @@
       <c r="I16" t="n">
         <v>1.59</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41481</v>
       </c>
       <c r="K16" t="n">
@@ -7807,13 +7819,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41590</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7840,7 +7852,7 @@
       <c r="I17" t="n">
         <v>1.84</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41590</v>
       </c>
       <c r="K17" t="n">
@@ -7853,13 +7865,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -7886,7 +7898,7 @@
       <c r="I18" t="n">
         <v>1.84</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="K18" t="n">
@@ -7899,13 +7911,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41761</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -7932,7 +7944,7 @@
       <c r="I19" t="n">
         <v>1.94</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41761</v>
       </c>
       <c r="K19" t="n">
@@ -7945,13 +7957,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41859</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -7978,7 +7990,7 @@
       <c r="I20" t="n">
         <v>2.74</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41859</v>
       </c>
       <c r="K20" t="n">
@@ -7991,13 +8003,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41950</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8024,7 +8036,7 @@
       <c r="I21" t="n">
         <v>2.7</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41950</v>
       </c>
       <c r="K21" t="n">
@@ -8037,13 +8049,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>42065</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8070,7 +8082,7 @@
       <c r="I22" t="n">
         <v>-4.6</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>42065</v>
       </c>
       <c r="K22" t="n">
@@ -8083,13 +8095,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8116,7 +8128,7 @@
       <c r="I23" t="n">
         <v>-4.07</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="K23" t="n">
@@ -8129,13 +8141,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8162,7 +8174,7 @@
       <c r="I24" t="n">
         <v>-3.26</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="K24" t="n">
@@ -8175,13 +8187,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8208,7 +8220,7 @@
       <c r="I25" t="n">
         <v>-3.34</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="K25" t="n">
@@ -8221,13 +8233,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8254,7 +8266,7 @@
       <c r="I26" t="n">
         <v>3.26</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="K26" t="n">
@@ -8267,13 +8279,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42499</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8300,7 +8312,7 @@
       <c r="I27" t="n">
         <v>1.46</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42499</v>
       </c>
       <c r="K27" t="n">
@@ -8313,13 +8325,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42590</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8346,7 +8358,7 @@
       <c r="I28" t="n">
         <v>1.07</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42590</v>
       </c>
       <c r="K28" t="n">
@@ -8359,13 +8371,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42678</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8392,7 +8404,7 @@
       <c r="I29" t="n">
         <v>1.08</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42678</v>
       </c>
       <c r="K29" t="n">
@@ -8405,13 +8417,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42793</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8438,7 +8450,7 @@
       <c r="I30" t="n">
         <v>1.76</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42793</v>
       </c>
       <c r="K30" t="n">
@@ -8451,13 +8463,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42860</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8484,7 +8496,7 @@
       <c r="I31" t="n">
         <v>2.79</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42860</v>
       </c>
       <c r="K31" t="n">
@@ -8497,13 +8509,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42951</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8530,7 +8542,7 @@
       <c r="I32" t="n">
         <v>2.73</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42951</v>
       </c>
       <c r="K32" t="n">
@@ -8543,13 +8555,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>43042</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8576,7 +8588,7 @@
       <c r="I33" t="n">
         <v>3.03</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>43042</v>
       </c>
       <c r="K33" t="n">
@@ -8589,13 +8601,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>43157</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8622,7 +8634,7 @@
       <c r="I34" t="n">
         <v>2.99</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>43157</v>
       </c>
       <c r="K34" t="n">
@@ -8635,13 +8647,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>43224</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8668,7 +8680,7 @@
       <c r="I35" t="n">
         <v>3.21</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>43224</v>
       </c>
       <c r="K35" t="n">
@@ -8681,13 +8693,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>43320</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8714,7 +8726,7 @@
       <c r="I36" t="n">
         <v>3.48</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>43320</v>
       </c>
       <c r="K36" t="n">
@@ -8727,13 +8739,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43406</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8760,7 +8772,7 @@
       <c r="I37" t="n">
         <v>4.01</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43406</v>
       </c>
       <c r="K37" t="n">
@@ -8773,13 +8785,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43518</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8806,7 +8818,7 @@
       <c r="I38" t="n">
         <v>4.550000000000001</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43518</v>
       </c>
       <c r="K38" t="n">
@@ -8819,13 +8831,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43588</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8852,7 +8864,7 @@
       <c r="I39" t="n">
         <v>5.2</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43588</v>
       </c>
       <c r="K39" t="n">
@@ -8865,13 +8877,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43679</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -8898,7 +8910,7 @@
       <c r="I40" t="n">
         <v>6.039999999999999</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43679</v>
       </c>
       <c r="K40" t="n">
@@ -8911,13 +8923,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -8944,7 +8956,7 @@
       <c r="I41" t="n">
         <v>5.899999999999999</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="K41" t="n">
@@ -8957,13 +8969,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43882</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -8990,7 +9002,7 @@
       <c r="I42" t="n">
         <v>5.999999999999999</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43882</v>
       </c>
       <c r="K42" t="n">
@@ -9003,13 +9015,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43958</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9036,7 +9048,7 @@
       <c r="I43" t="n">
         <v>5.94</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43958</v>
       </c>
       <c r="K43" t="n">
@@ -9049,13 +9061,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9082,7 +9094,7 @@
       <c r="I44" t="n">
         <v>5.77</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="K44" t="n">
@@ -9095,13 +9107,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9128,7 +9140,7 @@
       <c r="I45" t="n">
         <v>5.1</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="K45" t="n">
@@ -9141,13 +9153,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>44246</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9174,7 +9186,7 @@
       <c r="I46" t="n">
         <v>4.21</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>44246</v>
       </c>
       <c r="K46" t="n">
@@ -9187,13 +9199,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9220,7 +9232,7 @@
       <c r="I47" t="n">
         <v>4.57</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="K47" t="n">
@@ -9233,13 +9245,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44407</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9266,7 +9278,7 @@
       <c r="I48" t="n">
         <v>3.81</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44407</v>
       </c>
       <c r="K48" t="n">
@@ -9279,13 +9291,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44504</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9312,7 +9324,7 @@
       <c r="I49" t="n">
         <v>4.75</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44504</v>
       </c>
       <c r="K49" t="n">
@@ -9325,13 +9337,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44610</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9358,7 +9370,7 @@
       <c r="I50" t="n">
         <v>5.53</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44610</v>
       </c>
       <c r="K50" t="n">
@@ -9371,13 +9383,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9404,7 +9416,7 @@
       <c r="I51" t="n">
         <v>5.41</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="K51" t="n">
@@ -9417,13 +9429,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44771</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9450,7 +9462,7 @@
       <c r="I52" t="n">
         <v>7.020000000000001</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44771</v>
       </c>
       <c r="K52" t="n">
@@ -9463,13 +9475,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44869</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9496,7 +9508,7 @@
       <c r="I53" t="n">
         <v>7.640000000000001</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44869</v>
       </c>
       <c r="K53" t="n">
@@ -9509,13 +9521,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44974</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9542,7 +9554,7 @@
       <c r="I54" t="n">
         <v>7.67</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44974</v>
       </c>
       <c r="K54" t="n">
@@ -9555,13 +9567,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>45051</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9588,7 +9600,7 @@
       <c r="I55" t="n">
         <v>8.82</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>45051</v>
       </c>
       <c r="K55" t="n">
@@ -9601,13 +9613,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9634,7 +9646,7 @@
       <c r="I56" t="n">
         <v>8.66</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="K56" t="n">
@@ -9647,13 +9659,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>45226</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9680,7 +9692,7 @@
       <c r="I57" t="n">
         <v>9.290000000000001</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>45226</v>
       </c>
       <c r="K57" t="n">
@@ -9693,13 +9705,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>45338</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9726,7 +9738,7 @@
       <c r="I58" t="n">
         <v>10.31</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>45338</v>
       </c>
       <c r="K58" t="n">
@@ -9739,13 +9751,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45420</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9772,7 +9784,7 @@
       <c r="I59" t="n">
         <v>9.970000000000001</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45420</v>
       </c>
       <c r="K59" t="n">
@@ -9785,13 +9797,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45511</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9818,7 +9830,7 @@
       <c r="I60" t="n">
         <v>10.92</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45511</v>
       </c>
       <c r="K60" t="n">
@@ -9831,13 +9843,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45595</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9864,7 +9876,7 @@
       <c r="I61" t="n">
         <v>11.09</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45595</v>
       </c>
       <c r="K61" t="n">
@@ -9877,13 +9889,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45700</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -9910,7 +9922,7 @@
       <c r="I62" t="n">
         <v>8.500000000000002</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45700</v>
       </c>
       <c r="K62" t="n">
@@ -9923,13 +9935,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -9956,7 +9968,7 @@
       <c r="I63" t="n">
         <v>9.57</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="K63" t="n">
@@ -9969,13 +9981,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45868</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10002,7 +10014,7 @@
       <c r="I64" t="n">
         <v>10.16</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45868</v>
       </c>
       <c r="K64" t="n">
@@ -10015,13 +10027,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45959</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10048,7 +10060,7 @@
       <c r="I65" t="n">
         <v>10.87</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45959</v>
       </c>
       <c r="K65" t="n">
@@ -10061,13 +10073,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>46064</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10094,7 +10106,7 @@
       <c r="I66" t="n">
         <v>13.76</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>46064</v>
       </c>
       <c r="K66" t="n">
@@ -10107,13 +10119,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10140,7 +10152,7 @@
       <c r="I67" t="n">
         <v>14.46</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="K67" t="n">
@@ -10153,13 +10165,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>46232</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10186,7 +10198,7 @@
       <c r="I68" t="n">
         <v>15.54</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>46232</v>
       </c>
       <c r="K68" t="n">
@@ -10223,52 +10235,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40394</v>
       </c>
       <c r="C2" t="n">
@@ -10297,10 +10309,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40480</v>
       </c>
       <c r="C3" t="n">
@@ -10329,10 +10341,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40574</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="C4" t="n">
@@ -10361,10 +10373,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40662</v>
       </c>
       <c r="C5" t="n">
@@ -10393,10 +10405,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40753</v>
       </c>
       <c r="C6" t="n">
@@ -10425,10 +10437,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40844</v>
       </c>
       <c r="C7" t="n">
@@ -10457,10 +10469,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40939</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="C8" t="n">
@@ -10489,10 +10501,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>41026</v>
       </c>
       <c r="C9" t="n">
@@ -10521,10 +10533,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>41117</v>
       </c>
       <c r="C10" t="n">
@@ -10553,10 +10565,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>41219</v>
       </c>
       <c r="C11" t="n">
@@ -10585,10 +10597,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41305</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41331</v>
       </c>
       <c r="C12" t="n">
@@ -10617,10 +10629,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41390</v>
       </c>
       <c r="C13" t="n">
@@ -10649,10 +10661,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41481</v>
       </c>
       <c r="C14" t="n">
@@ -10681,10 +10693,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41590</v>
       </c>
       <c r="C15" t="n">
@@ -10713,10 +10725,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41670</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="C16" t="n">
@@ -10745,10 +10757,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41761</v>
       </c>
       <c r="C17" t="n">
@@ -10777,10 +10789,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41859</v>
       </c>
       <c r="C18" t="n">
@@ -10809,10 +10821,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41950</v>
       </c>
       <c r="C19" t="n">
@@ -10841,10 +10853,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>42035</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>42065</v>
       </c>
       <c r="C20" t="n">
@@ -10873,10 +10885,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="C21" t="n">
@@ -10905,10 +10917,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="C22" t="n">
@@ -10937,10 +10949,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="C23" t="n">
@@ -10969,10 +10981,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42398</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="C24" t="n">
@@ -11001,10 +11013,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42499</v>
       </c>
       <c r="C25" t="n">
@@ -11033,10 +11045,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42587</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42590</v>
       </c>
       <c r="C26" t="n">
@@ -11065,10 +11077,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42677</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42678</v>
       </c>
       <c r="C27" t="n">
@@ -11097,10 +11109,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42790</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42793</v>
       </c>
       <c r="C28" t="n">
@@ -11129,10 +11141,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42859</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42860</v>
       </c>
       <c r="C29" t="n">
@@ -11161,10 +11173,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42950</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42951</v>
       </c>
       <c r="C30" t="n">
@@ -11193,10 +11205,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>43041</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>43042</v>
       </c>
       <c r="C31" t="n">
@@ -11225,10 +11237,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>43154</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>43157</v>
       </c>
       <c r="C32" t="n">
@@ -11257,10 +11269,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>43223</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>43224</v>
       </c>
       <c r="C33" t="n">
@@ -11289,10 +11301,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43319</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43320</v>
       </c>
       <c r="C34" t="n">
@@ -11321,10 +11333,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43405</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43406</v>
       </c>
       <c r="C35" t="n">
@@ -11353,10 +11365,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43517</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43518</v>
       </c>
       <c r="C36" t="n">
@@ -11385,10 +11397,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43587</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43588</v>
       </c>
       <c r="C37" t="n">
@@ -11417,10 +11429,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43678</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43679</v>
       </c>
       <c r="C38" t="n">
@@ -11449,10 +11461,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43769</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="C39" t="n">
@@ -11481,10 +11493,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43881</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43882</v>
       </c>
       <c r="C40" t="n">
@@ -11513,10 +11525,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43957</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43958</v>
       </c>
       <c r="C41" t="n">
@@ -11545,10 +11557,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>44042</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="C42" t="n">
@@ -11577,10 +11589,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>44133</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="C43" t="n">
@@ -11609,10 +11621,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44245</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>44246</v>
       </c>
       <c r="C44" t="n">
@@ -11641,10 +11653,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44315</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="C45" t="n">
@@ -11673,10 +11685,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44406</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44407</v>
       </c>
       <c r="C46" t="n">
@@ -11705,10 +11717,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44503</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44504</v>
       </c>
       <c r="C47" t="n">
@@ -11737,10 +11749,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44609</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44610</v>
       </c>
       <c r="C48" t="n">
@@ -11769,10 +11781,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44679</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="C49" t="n">
@@ -11801,10 +11813,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44770</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44771</v>
       </c>
       <c r="C50" t="n">
@@ -11833,10 +11845,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44868</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44869</v>
       </c>
       <c r="C51" t="n">
@@ -11865,10 +11877,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44973</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44974</v>
       </c>
       <c r="C52" t="n">
@@ -11897,10 +11909,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44981</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44984</v>
       </c>
       <c r="C53" t="n">
@@ -11929,10 +11941,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>45050</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>45051</v>
       </c>
       <c r="C54" t="n">
@@ -11961,10 +11973,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45141</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="C55" t="n">
@@ -11993,10 +12005,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45225</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45226</v>
       </c>
       <c r="C56" t="n">
@@ -12025,10 +12037,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45337</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45338</v>
       </c>
       <c r="C57" t="n">
@@ -12057,10 +12069,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45419</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45420</v>
       </c>
       <c r="C58" t="n">
@@ -12089,10 +12101,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45510</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45511</v>
       </c>
       <c r="C59" t="n">
@@ -12121,10 +12133,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45594</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45595</v>
       </c>
       <c r="C60" t="n">
@@ -12153,10 +12165,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45699</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45700</v>
       </c>
       <c r="C61" t="n">
@@ -12185,10 +12197,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45776</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="C62" t="n">
@@ -12217,10 +12229,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45867</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45868</v>
       </c>
       <c r="C63" t="n">
@@ -12249,10 +12261,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45958</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45959</v>
       </c>
       <c r="C64" t="n">
@@ -12281,10 +12293,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>46063</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>46064</v>
       </c>
       <c r="C65" t="n">
@@ -12313,10 +12325,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>46140</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="C66" t="n">
@@ -12345,10 +12357,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>46231</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>46232</v>
       </c>
       <c r="C67" t="n">
@@ -12395,12 +12407,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -12471,7 +12483,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8">

--- a/salidas/empresas/EQIX.xlsx
+++ b/salidas/empresas/EQIX.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>34.35152435302734</v>
+        <v>34.35151290893555</v>
       </c>
       <c r="C2" t="n">
         <v>46.93000030517578</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>38.38469314575195</v>
+        <v>38.38468170166016</v>
       </c>
       <c r="C3" t="n">
         <v>52.43999862670898</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>47.00733184814453</v>
+        <v>47.00734329223633</v>
       </c>
       <c r="C4" t="n">
         <v>64.22000122070312</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>48.23705291748047</v>
+        <v>48.237060546875</v>
       </c>
       <c r="C5" t="n">
         <v>65.90000152587891</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>42.659423828125</v>
+        <v>42.65942001342773</v>
       </c>
       <c r="C6" t="n">
         <v>58.27999877929688</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>38.34078979492188</v>
+        <v>38.34078216552734</v>
       </c>
       <c r="C8" t="n">
         <v>52.38000106811523</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>42.21290969848633</v>
+        <v>42.21291732788086</v>
       </c>
       <c r="C9" t="n">
         <v>57.66999816894531</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>50.06698226928711</v>
+        <v>50.06698608398438</v>
       </c>
       <c r="C11" t="n">
         <v>68.40000152587891</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>56.0032958984375</v>
+        <v>56.0033073425293</v>
       </c>
       <c r="C12" t="n">
         <v>76.51000213623047</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>55.35182952880859</v>
+        <v>55.3518180847168</v>
       </c>
       <c r="C13" t="n">
         <v>75.62000274658203</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>61.53702926635742</v>
+        <v>61.53700637817383</v>
       </c>
       <c r="C14" t="n">
         <v>84.06999969482422</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>60.51224136352539</v>
+        <v>60.51227188110352</v>
       </c>
       <c r="C15" t="n">
         <v>82.66999816894531</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>62.67890167236328</v>
+        <v>62.67890548706055</v>
       </c>
       <c r="C16" t="n">
         <v>85.62999725341797</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>61.09783554077148</v>
+        <v>61.09782409667969</v>
       </c>
       <c r="C17" t="n">
         <v>83.47000122070312</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>63.95985412597656</v>
+        <v>63.95984268188477</v>
       </c>
       <c r="C18" t="n">
         <v>87.37999725341797</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>66.95363616943359</v>
+        <v>66.95361328125</v>
       </c>
       <c r="C19" t="n">
         <v>91.47000122070312</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>63.61582183837891</v>
+        <v>63.61582565307617</v>
       </c>
       <c r="C20" t="n">
         <v>86.91000366210938</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>64.78696441650391</v>
+        <v>64.78695678710938</v>
       </c>
       <c r="C21" t="n">
         <v>88.51000213623047</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>85.39203643798828</v>
+        <v>85.39206695556641</v>
       </c>
       <c r="C23" t="n">
         <v>116.6600036621094</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>76.20577239990234</v>
+        <v>76.20578002929688</v>
       </c>
       <c r="C24" t="n">
         <v>104.1100006103516</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>73.98058319091797</v>
+        <v>73.98056793212891</v>
       </c>
       <c r="C25" t="n">
         <v>101.0699996948242</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>55.28595352172852</v>
+        <v>55.28598785400391</v>
       </c>
       <c r="C26" t="n">
         <v>75.52999877929688</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>50.76236724853516</v>
+        <v>50.76237106323242</v>
       </c>
       <c r="C27" t="n">
         <v>69.34999847412109</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>48.66893768310547</v>
+        <v>48.66892242431641</v>
       </c>
       <c r="C28" t="n">
         <v>66.48999786376953</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>66.18503570556641</v>
+        <v>66.18505859375</v>
       </c>
       <c r="C29" t="n">
         <v>90.41999816894531</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>69.89617156982422</v>
+        <v>69.89615631103516</v>
       </c>
       <c r="C30" t="n">
         <v>95.48999786376953</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>65.30669403076172</v>
+        <v>65.30667877197266</v>
       </c>
       <c r="C31" t="n">
         <v>89.22000122070312</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>58.92388153076172</v>
+        <v>58.92387390136719</v>
       </c>
       <c r="C33" t="n">
         <v>80.5</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>50.84289169311523</v>
+        <v>50.84288024902344</v>
       </c>
       <c r="C34" t="n">
         <v>69.45999908447266</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>33.23892593383789</v>
+        <v>33.23892211914062</v>
       </c>
       <c r="C36" t="n">
         <v>45.40999984741211</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>38.93367767333984</v>
+        <v>38.93367004394531</v>
       </c>
       <c r="C37" t="n">
         <v>53.18999862670898</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>51.4065055847168</v>
+        <v>51.40650939941406</v>
       </c>
       <c r="C41" t="n">
         <v>70.23000335693359</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>53.24375152587891</v>
+        <v>53.2437629699707</v>
       </c>
       <c r="C43" t="n">
         <v>72.73999786376953</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>59.82419204711914</v>
+        <v>59.82420349121094</v>
       </c>
       <c r="C44" t="n">
         <v>81.73000335693359</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>61.75661087036133</v>
+        <v>61.75662994384766</v>
       </c>
       <c r="C45" t="n">
         <v>84.37000274658203</v>
@@ -1334,7 +1334,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>67.34158325195312</v>
+        <v>67.34156036376953</v>
       </c>
       <c r="C46" t="n">
         <v>92</v>
@@ -1353,7 +1353,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>62.45199203491211</v>
+        <v>62.45198059082031</v>
       </c>
       <c r="C47" t="n">
         <v>85.31999969482422</v>
@@ -1372,7 +1372,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>70.40852355957031</v>
+        <v>70.40853118896484</v>
       </c>
       <c r="C48" t="n">
         <v>96.19000244140625</v>
@@ -1410,7 +1410,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>70.43782806396484</v>
+        <v>70.43780517578125</v>
       </c>
       <c r="C50" t="n">
         <v>96.23000335693359</v>
@@ -1429,7 +1429,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>69.14952087402344</v>
+        <v>69.14952850341797</v>
       </c>
       <c r="C51" t="n">
         <v>94.47000122070312</v>
@@ -1448,7 +1448,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>71.25030517578125</v>
+        <v>71.25029754638672</v>
       </c>
       <c r="C52" t="n">
         <v>97.33999633789062</v>
@@ -1486,7 +1486,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>67.34889984130859</v>
+        <v>67.34890747070312</v>
       </c>
       <c r="C54" t="n">
         <v>92.01000213623047</v>
@@ -1524,7 +1524,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>68.44685363769531</v>
+        <v>68.44683837890625</v>
       </c>
       <c r="C56" t="n">
         <v>93.51000213623047</v>
@@ -1543,7 +1543,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>66.76332855224609</v>
+        <v>66.76332092285156</v>
       </c>
       <c r="C57" t="n">
         <v>91.20999908447266</v>
@@ -1568,7 +1568,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>74.91750335693359</v>
+        <v>74.91748046875</v>
       </c>
       <c r="C58" t="n">
         <v>102.3499984741211</v>
@@ -1593,7 +1593,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>61.66144943237305</v>
+        <v>61.66147232055664</v>
       </c>
       <c r="C59" t="n">
         <v>84.23999786376953</v>
@@ -1618,7 +1618,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>56.80112457275391</v>
+        <v>56.80113220214844</v>
       </c>
       <c r="C60" t="n">
         <v>77.59999847412109</v>
@@ -1643,7 +1643,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>59.48017501831055</v>
+        <v>59.48018646240234</v>
       </c>
       <c r="C61" t="n">
         <v>81.26000213623047</v>
@@ -1718,7 +1718,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>66.68277740478516</v>
+        <v>66.68279266357422</v>
       </c>
       <c r="C64" t="n">
         <v>91.09999847412109</v>
@@ -1743,7 +1743,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>73.68044281005859</v>
+        <v>73.68048095703125</v>
       </c>
       <c r="C65" t="n">
         <v>100.6600036621094</v>
@@ -1768,7 +1768,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>74.22210693359375</v>
+        <v>74.22212982177734</v>
       </c>
       <c r="C66" t="n">
         <v>101.4000015258789</v>
@@ -1818,7 +1818,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>76.46926116943359</v>
+        <v>76.46927642822266</v>
       </c>
       <c r="C68" t="n">
         <v>104.4700012207031</v>
@@ -1843,7 +1843,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>68.83477783203125</v>
+        <v>68.83479309082031</v>
       </c>
       <c r="C69" t="n">
         <v>94.04000091552734</v>
@@ -1868,7 +1868,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>65.02121734619141</v>
+        <v>65.02122497558594</v>
       </c>
       <c r="C70" t="n">
         <v>88.83000183105469</v>
@@ -1893,7 +1893,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>70.27677917480469</v>
+        <v>70.27677154541016</v>
       </c>
       <c r="C71" t="n">
         <v>96.01000213623047</v>
@@ -1918,7 +1918,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>73.21199035644531</v>
+        <v>73.21196746826172</v>
       </c>
       <c r="C72" t="n">
         <v>100.0199966430664</v>
@@ -1943,7 +1943,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>74.22210693359375</v>
+        <v>74.22212982177734</v>
       </c>
       <c r="C73" t="n">
         <v>101.4000015258789</v>
@@ -1968,7 +1968,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>87.80754852294922</v>
+        <v>87.80754089355469</v>
       </c>
       <c r="C74" t="n">
         <v>119.9599990844727</v>
@@ -1993,7 +1993,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>102.608039855957</v>
+        <v>102.6080703735352</v>
       </c>
       <c r="C75" t="n">
         <v>140.1799926757812</v>
@@ -2022,7 +2022,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>115.2491912841797</v>
+        <v>115.2492446899414</v>
       </c>
       <c r="C76" t="n">
         <v>157.4499969482422</v>
@@ -2051,7 +2051,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>120.1900405883789</v>
+        <v>120.190071105957</v>
       </c>
       <c r="C77" t="n">
         <v>164.1999969482422</v>
@@ -2109,7 +2109,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>128.5711059570312</v>
+        <v>128.5711822509766</v>
       </c>
       <c r="C79" t="n">
         <v>175.6499938964844</v>
@@ -2138,7 +2138,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>130.4230041503906</v>
+        <v>130.4230804443359</v>
       </c>
       <c r="C80" t="n">
         <v>178.1799926757812</v>
@@ -2167,7 +2167,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>144.6746215820312</v>
+        <v>144.6745758056641</v>
       </c>
       <c r="C81" t="n">
         <v>197.6499938964844</v>
@@ -2196,7 +2196,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>150.8231201171875</v>
+        <v>150.8231353759766</v>
       </c>
       <c r="C82" t="n">
         <v>206.0500030517578</v>
@@ -2225,7 +2225,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>132.1871337890625</v>
+        <v>132.1871185302734</v>
       </c>
       <c r="C83" t="n">
         <v>180.5899963378906</v>
@@ -2254,7 +2254,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>135.9713897705078</v>
+        <v>135.9713592529297</v>
       </c>
       <c r="C84" t="n">
         <v>185.7599945068359</v>
@@ -2283,7 +2283,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>150.9329223632812</v>
+        <v>150.9328765869141</v>
       </c>
       <c r="C85" t="n">
         <v>206.1999969482422</v>
@@ -2312,7 +2312,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>157.6890869140625</v>
+        <v>157.6890563964844</v>
       </c>
       <c r="C86" t="n">
         <v>215.4299926757812</v>
@@ -2341,7 +2341,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>154.8489685058594</v>
+        <v>154.8489837646484</v>
       </c>
       <c r="C87" t="n">
         <v>211.5500030517578</v>
@@ -2370,7 +2370,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>158.3332214355469</v>
+        <v>158.3331451416016</v>
       </c>
       <c r="C88" t="n">
         <v>216.3099975585938</v>
@@ -2399,7 +2399,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>156.7155151367188</v>
+        <v>156.7155609130859</v>
       </c>
       <c r="C89" t="n">
         <v>214.1000061035156</v>
@@ -2428,7 +2428,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>148.3271331787109</v>
+        <v>148.3270874023438</v>
       </c>
       <c r="C90" t="n">
         <v>202.6399993896484</v>
@@ -2457,7 +2457,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>135.2101745605469</v>
+        <v>135.2101440429688</v>
       </c>
       <c r="C91" t="n">
         <v>184.7200012207031</v>
@@ -2486,7 +2486,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>131.2794952392578</v>
+        <v>131.2794647216797</v>
       </c>
       <c r="C92" t="n">
         <v>179.3500061035156</v>
@@ -2515,7 +2515,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>127.1731033325195</v>
+        <v>127.1731109619141</v>
       </c>
       <c r="C93" t="n">
         <v>173.7400054931641</v>
@@ -2544,7 +2544,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>134.4269714355469</v>
+        <v>134.4269104003906</v>
       </c>
       <c r="C94" t="n">
         <v>183.6499938964844</v>
@@ -2573,7 +2573,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>118.0307235717773</v>
+        <v>118.0307464599609</v>
       </c>
       <c r="C95" t="n">
         <v>161.25</v>
@@ -2689,7 +2689,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>139.0457458496094</v>
+        <v>139.0457305908203</v>
       </c>
       <c r="C99" t="n">
         <v>189.9600067138672</v>
@@ -2718,7 +2718,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>135.2979583740234</v>
+        <v>135.2979125976562</v>
       </c>
       <c r="C100" t="n">
         <v>184.8399963378906</v>
@@ -2747,7 +2747,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>137.4719696044922</v>
+        <v>137.471923828125</v>
       </c>
       <c r="C101" t="n">
         <v>187.8099975585938</v>
@@ -2776,7 +2776,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>145.4797515869141</v>
+        <v>145.4797210693359</v>
       </c>
       <c r="C102" t="n">
         <v>198.75</v>
@@ -2805,7 +2805,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>153.7803039550781</v>
+        <v>153.7803497314453</v>
       </c>
       <c r="C103" t="n">
         <v>210.0899963378906</v>
@@ -2834,7 +2834,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>157.0229797363281</v>
+        <v>157.0229949951172</v>
       </c>
       <c r="C104" t="n">
         <v>214.5200042724609</v>
@@ -2863,7 +2863,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>159.7605590820312</v>
+        <v>159.7605285644531</v>
       </c>
       <c r="C105" t="n">
         <v>218.2599945068359</v>
@@ -2892,7 +2892,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>155.5297698974609</v>
+        <v>155.5297546386719</v>
       </c>
       <c r="C106" t="n">
         <v>212.4799957275391</v>
@@ -2950,7 +2950,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>172.8081970214844</v>
+        <v>172.8082275390625</v>
       </c>
       <c r="C108" t="n">
         <v>227.1699981689453</v>
@@ -2979,7 +2979,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>172.4734954833984</v>
+        <v>172.4735260009766</v>
       </c>
       <c r="C109" t="n">
         <v>226.7299957275391</v>
@@ -3037,7 +3037,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>170.5337219238281</v>
+        <v>170.5337371826172</v>
       </c>
       <c r="C111" t="n">
         <v>224.1799926757812</v>
@@ -3147,7 +3147,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>195.8482971191406</v>
+        <v>195.8482666015625</v>
       </c>
       <c r="C115" t="n">
         <v>254</v>
@@ -3174,7 +3174,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>215.0552825927734</v>
+        <v>215.0553283691406</v>
       </c>
       <c r="C116" t="n">
         <v>278.9100036621094</v>
@@ -3201,7 +3201,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>209.3115997314453</v>
+        <v>209.3115844726562</v>
       </c>
       <c r="C117" t="n">
         <v>269.7699890136719</v>
@@ -3228,7 +3228,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>212.1281433105469</v>
+        <v>212.1281280517578</v>
       </c>
       <c r="C118" t="n">
         <v>273.3999938964844</v>
@@ -3255,7 +3255,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>239.4410858154297</v>
+        <v>239.4410400390625</v>
       </c>
       <c r="C119" t="n">
         <v>296.6799926757812</v>
@@ -3282,7 +3282,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>239.2957916259766</v>
+        <v>239.2957611083984</v>
       </c>
       <c r="C120" t="n">
         <v>296.5</v>
@@ -3309,7 +3309,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>245.4346313476562</v>
+        <v>245.4345245361328</v>
       </c>
       <c r="C121" t="n">
         <v>302.3999938964844</v>
@@ -3336,7 +3336,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>252.0654296875</v>
+        <v>252.0655364990234</v>
       </c>
       <c r="C122" t="n">
         <v>310.5700073242188</v>
@@ -3363,7 +3363,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>246.4815063476562</v>
+        <v>246.4816589355469</v>
       </c>
       <c r="C123" t="n">
         <v>303.6900024414062</v>
@@ -3392,7 +3392,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>269.9367370605469</v>
+        <v>269.9367980957031</v>
       </c>
       <c r="C124" t="n">
         <v>330.7099914550781</v>
@@ -3421,7 +3421,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>269.64306640625</v>
+        <v>269.6430358886719</v>
       </c>
       <c r="C125" t="n">
         <v>330.3500061035156</v>
@@ -3450,7 +3450,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>296.9832763671875</v>
+        <v>296.9831237792969</v>
       </c>
       <c r="C126" t="n">
         <v>362</v>
@@ -3479,7 +3479,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>318.0919494628906</v>
+        <v>318.0920104980469</v>
       </c>
       <c r="C127" t="n">
         <v>387.7300109863281</v>
@@ -3508,7 +3508,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>305.9007873535156</v>
+        <v>305.9010314941406</v>
       </c>
       <c r="C128" t="n">
         <v>372.8699951171875</v>
@@ -3537,7 +3537,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>303.8905944824219</v>
+        <v>303.8905639648438</v>
       </c>
       <c r="C129" t="n">
         <v>368.6499938964844</v>
@@ -3595,7 +3595,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>294.5180053710938</v>
+        <v>294.5179748535156</v>
       </c>
       <c r="C131" t="n">
         <v>357.2799987792969</v>
@@ -3624,7 +3624,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>280.7628479003906</v>
+        <v>280.7628784179688</v>
       </c>
       <c r="C132" t="n">
         <v>338.760009765625</v>
@@ -3653,7 +3653,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>296.2199401855469</v>
+        <v>296.2198181152344</v>
       </c>
       <c r="C133" t="n">
         <v>357.4100036621094</v>
@@ -3682,7 +3682,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>319.0698852539062</v>
+        <v>319.06982421875</v>
       </c>
       <c r="C134" t="n">
         <v>384.9800109863281</v>
@@ -3711,7 +3711,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>313.3641052246094</v>
+        <v>313.3639831542969</v>
       </c>
       <c r="C135" t="n">
         <v>376.0700073242188</v>
@@ -3769,7 +3769,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>348.0526733398438</v>
+        <v>348.0526123046875</v>
       </c>
       <c r="C137" t="n">
         <v>417.7000122070312</v>
@@ -3827,7 +3827,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>359.2857055664062</v>
+        <v>359.2856750488281</v>
       </c>
       <c r="C139" t="n">
         <v>429.1600036621094</v>
@@ -3885,7 +3885,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>393.8957214355469</v>
+        <v>393.8958435058594</v>
       </c>
       <c r="C141" t="n">
         <v>468.4100036621094</v>
@@ -3943,7 +3943,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>389.7669067382812</v>
+        <v>389.7667846679688</v>
       </c>
       <c r="C143" t="n">
         <v>463.5</v>
@@ -3972,7 +3972,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>392.2197265625</v>
+        <v>392.2196350097656</v>
       </c>
       <c r="C144" t="n">
         <v>464.489990234375</v>
@@ -4001,7 +4001,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>382.7032165527344</v>
+        <v>382.7031555175781</v>
       </c>
       <c r="C145" t="n">
         <v>453.2200012207031</v>
@@ -4030,7 +4030,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>384.3667602539062</v>
+        <v>384.3664855957031</v>
       </c>
       <c r="C146" t="n">
         <v>455.1900024414062</v>
@@ -4059,7 +4059,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>333.0376586914062</v>
+        <v>333.0376892089844</v>
       </c>
       <c r="C147" t="n">
         <v>392.1000061035156</v>
@@ -4088,7 +4088,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>355.1552124023438</v>
+        <v>355.1552429199219</v>
       </c>
       <c r="C148" t="n">
         <v>418.1400146484375</v>
@@ -4117,7 +4117,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>357.4060668945312</v>
+        <v>357.4060974121094</v>
       </c>
       <c r="C149" t="n">
         <v>420.7900085449219</v>
@@ -4146,7 +4146,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>339.0606689453125</v>
+        <v>339.0606994628906</v>
       </c>
       <c r="C150" t="n">
         <v>396.8500061035156</v>
@@ -4175,7 +4175,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>367.2894592285156</v>
+        <v>367.2894897460938</v>
       </c>
       <c r="C151" t="n">
         <v>429.8900146484375</v>
@@ -4204,7 +4204,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>375.3121032714844</v>
+        <v>375.3120727539062</v>
       </c>
       <c r="C152" t="n">
         <v>439.2799987792969</v>
@@ -4233,7 +4233,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>374.5691528320312</v>
+        <v>374.5691833496094</v>
       </c>
       <c r="C153" t="n">
         <v>436.1300048828125</v>
@@ -4262,7 +4262,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>371.7864990234375</v>
+        <v>371.7864074707031</v>
       </c>
       <c r="C154" t="n">
         <v>432.8900146484375</v>
@@ -4291,7 +4291,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>325.2798461914062</v>
+        <v>325.2798156738281</v>
       </c>
       <c r="C155" t="n">
         <v>378.739990234375</v>
@@ -4320,7 +4320,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>332.8454284667969</v>
+        <v>332.845458984375</v>
       </c>
       <c r="C156" t="n">
         <v>385.2799987792969</v>
@@ -4349,7 +4349,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>304.5785217285156</v>
+        <v>304.5784606933594</v>
       </c>
       <c r="C157" t="n">
         <v>352.5599975585938</v>
@@ -4407,7 +4407,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>367.9740905761719</v>
+        <v>367.9741516113281</v>
       </c>
       <c r="C159" t="n">
         <v>423.5</v>
@@ -4465,7 +4465,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>395.0834655761719</v>
+        <v>395.0834045410156</v>
       </c>
       <c r="C161" t="n">
         <v>454.7000122070312</v>
@@ -4494,7 +4494,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>424.2709655761719</v>
+        <v>424.2710266113281</v>
       </c>
       <c r="C162" t="n">
         <v>485.7900085449219</v>
@@ -4523,7 +4523,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>440.42822265625</v>
+        <v>440.4282836914062</v>
       </c>
       <c r="C163" t="n">
         <v>504.2900085449219</v>
@@ -4552,7 +4552,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>438.515625</v>
+        <v>438.5155334472656</v>
       </c>
       <c r="C164" t="n">
         <v>502.1000061035156</v>
@@ -4610,7 +4610,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>505.9954833984375</v>
+        <v>505.9955444335938</v>
       </c>
       <c r="C166" t="n">
         <v>576.7999877929688</v>
@@ -4639,7 +4639,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>497.2057495117188</v>
+        <v>497.205810546875</v>
       </c>
       <c r="C167" t="n">
         <v>566.780029296875</v>
@@ -4668,7 +4668,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>499.4681091308594</v>
+        <v>499.4681701660156</v>
       </c>
       <c r="C168" t="n">
         <v>566.8499755859375</v>
@@ -4697,7 +4697,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>514.315185546875</v>
+        <v>514.3152465820312</v>
       </c>
       <c r="C169" t="n">
         <v>583.7000122070312</v>
@@ -4726,7 +4726,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>519.6282958984375</v>
+        <v>519.6285400390625</v>
       </c>
       <c r="C170" t="n">
         <v>589.72998046875</v>
@@ -4755,7 +4755,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>506.8013305664062</v>
+        <v>506.80126953125</v>
       </c>
       <c r="C171" t="n">
         <v>572.7999877929688</v>
@@ -4784,7 +4784,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>552.6065063476562</v>
+        <v>552.606201171875</v>
       </c>
       <c r="C172" t="n">
         <v>624.5700073242188</v>
@@ -4813,7 +4813,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>597.402587890625</v>
+        <v>597.4026489257812</v>
       </c>
       <c r="C173" t="n">
         <v>675.2000122070312</v>
@@ -4842,7 +4842,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>619.73681640625</v>
+        <v>619.7369384765625</v>
       </c>
       <c r="C174" t="n">
         <v>697.6300048828125</v>
@@ -4900,7 +4900,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>697.778076171875</v>
+        <v>697.7781982421875</v>
       </c>
       <c r="C176" t="n">
         <v>785.47998046875</v>
@@ -4929,7 +4929,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>704.0234375</v>
+        <v>704.0236206054688</v>
       </c>
       <c r="C177" t="n">
         <v>789.780029296875</v>
@@ -4958,7 +4958,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>677.5931396484375</v>
+        <v>677.5930786132812</v>
       </c>
       <c r="C178" t="n">
         <v>760.1300048828125</v>
@@ -4987,7 +4987,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>651.8399658203125</v>
+        <v>651.840087890625</v>
       </c>
       <c r="C179" t="n">
         <v>731.239990234375</v>
@@ -5016,7 +5016,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>624.2210083007812</v>
+        <v>624.2211303710938</v>
       </c>
       <c r="C180" t="n">
         <v>697.7899780273438</v>
@@ -5045,7 +5045,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>638.883056640625</v>
+        <v>638.8831176757812</v>
       </c>
       <c r="C181" t="n">
         <v>714.1799926757812</v>
@@ -5074,7 +5074,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>661.9451904296875</v>
+        <v>661.9451293945312</v>
       </c>
       <c r="C182" t="n">
         <v>739.9600219726562</v>
@@ -5103,7 +5103,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>582.4898071289062</v>
+        <v>582.4896240234375</v>
       </c>
       <c r="C183" t="n">
         <v>648.3400268554688</v>
@@ -5132,7 +5132,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>610.5657348632812</v>
+        <v>610.56591796875</v>
       </c>
       <c r="C184" t="n">
         <v>679.5900268554688</v>
@@ -5161,7 +5161,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>647.5540771484375</v>
+        <v>647.5543823242188</v>
       </c>
       <c r="C185" t="n">
         <v>720.760009765625</v>
@@ -5190,7 +5190,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>664.5604858398438</v>
+        <v>664.5606079101562</v>
       </c>
       <c r="C186" t="n">
         <v>736.719970703125</v>
@@ -5219,7 +5219,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>723.9879150390625</v>
+        <v>723.98779296875</v>
       </c>
       <c r="C187" t="n">
         <v>802.5999755859375</v>
@@ -5248,7 +5248,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>740.0535888671875</v>
+        <v>740.0535278320312</v>
       </c>
       <c r="C188" t="n">
         <v>820.4099731445312</v>
@@ -5277,7 +5277,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>763.4993896484375</v>
+        <v>763.499267578125</v>
       </c>
       <c r="C189" t="n">
         <v>843.4500122070312</v>
@@ -5306,7 +5306,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>715.2337036132812</v>
+        <v>715.2335205078125</v>
       </c>
       <c r="C190" t="n">
         <v>790.1300048828125</v>
@@ -5335,7 +5335,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>757.7241821289062</v>
+        <v>757.72412109375</v>
       </c>
       <c r="C191" t="n">
         <v>837.0700073242188</v>
@@ -5364,7 +5364,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>737.8659057617188</v>
+        <v>737.8658447265625</v>
       </c>
       <c r="C192" t="n">
         <v>812.2000122070312</v>
@@ -5393,7 +5393,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>768.427001953125</v>
+        <v>768.4271850585938</v>
       </c>
       <c r="C193" t="n">
         <v>845.8400268554688</v>
@@ -5451,7 +5451,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>644.7740478515625</v>
+        <v>644.7741088867188</v>
       </c>
       <c r="C195" t="n">
         <v>709.72998046875</v>
@@ -5480,7 +5480,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>676.6556396484375</v>
+        <v>676.6555786132812</v>
       </c>
       <c r="C196" t="n">
         <v>741.6199951171875</v>
@@ -5509,7 +5509,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>656.0901489257812</v>
+        <v>656.0900268554688</v>
       </c>
       <c r="C197" t="n">
         <v>719.0800170898438</v>
@@ -5538,7 +5538,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>629.9232177734375</v>
+        <v>629.9232788085938</v>
       </c>
       <c r="C198" t="n">
         <v>687.0900268554688</v>
@@ -5596,7 +5596,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>645.1879272460938</v>
+        <v>645.1878662109375</v>
       </c>
       <c r="C200" t="n">
         <v>703.739990234375</v>
@@ -5625,7 +5625,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>605.3009643554688</v>
+        <v>605.301025390625</v>
       </c>
       <c r="C201" t="n">
         <v>657.3699951171875</v>
@@ -5683,7 +5683,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>521.573486328125</v>
+        <v>521.5735473632812</v>
       </c>
       <c r="C203" t="n">
         <v>566.4400024414062</v>
@@ -5712,7 +5712,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>639.0455932617188</v>
+        <v>639.0457153320312</v>
       </c>
       <c r="C204" t="n">
         <v>690.6500244140625</v>
@@ -5741,7 +5741,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>606.0870361328125</v>
+        <v>606.0870971679688</v>
       </c>
       <c r="C205" t="n">
         <v>655.030029296875</v>
@@ -5770,7 +5770,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>682.9779052734375</v>
+        <v>682.9779663085938</v>
       </c>
       <c r="C206" t="n">
         <v>738.1300048828125</v>
@@ -5799,7 +5799,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>636.843505859375</v>
+        <v>636.8434448242188</v>
       </c>
       <c r="C207" t="n">
         <v>688.27001953125</v>
@@ -5886,7 +5886,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>696.4625854492188</v>
+        <v>696.4624633789062</v>
       </c>
       <c r="C210" t="n">
         <v>745.5499877929688</v>
@@ -5915,7 +5915,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>732.3248291015625</v>
+        <v>732.3248901367188</v>
       </c>
       <c r="C211" t="n">
         <v>783.9400024414062</v>
@@ -5973,7 +5973,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>733.286376953125</v>
+        <v>733.2864379882812</v>
       </c>
       <c r="C213" t="n">
         <v>781.3800048828125</v>
@@ -6002,7 +6002,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>681.55908203125</v>
+        <v>681.5591430664062</v>
       </c>
       <c r="C214" t="n">
         <v>726.260009765625</v>
@@ -6031,7 +6031,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>684.7310791015625</v>
+        <v>684.73095703125</v>
       </c>
       <c r="C215" t="n">
         <v>729.6400146484375</v>
@@ -6060,7 +6060,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>769.1433715820312</v>
+        <v>769.1434326171875</v>
       </c>
       <c r="C216" t="n">
         <v>815.010009765625</v>
@@ -6118,7 +6118,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>783.0728149414062</v>
+        <v>783.07275390625</v>
       </c>
       <c r="C218" t="n">
         <v>829.77001953125</v>
@@ -6176,7 +6176,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>782.6817016601562</v>
+        <v>782.6817626953125</v>
       </c>
       <c r="C220" t="n">
         <v>825.3300170898438</v>
@@ -6205,7 +6205,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>674.3639526367188</v>
+        <v>674.364013671875</v>
       </c>
       <c r="C221" t="n">
         <v>711.1099853515625</v>
@@ -6234,7 +6234,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>727.4503173828125</v>
+        <v>727.4502563476562</v>
       </c>
       <c r="C222" t="n">
         <v>762.97998046875</v>
@@ -6263,7 +6263,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>721.3673706054688</v>
+        <v>721.367431640625</v>
       </c>
       <c r="C223" t="n">
         <v>756.5999755859375</v>
@@ -6292,7 +6292,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>753.44091796875</v>
+        <v>753.4408569335938</v>
       </c>
       <c r="C224" t="n">
         <v>790.239990234375</v>
@@ -6350,7 +6350,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>850.6626586914062</v>
+        <v>850.66259765625</v>
       </c>
       <c r="C226" t="n">
         <v>887.6300048828125</v>
@@ -6437,7 +6437,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>907.904296875</v>
+        <v>907.9042358398438</v>
       </c>
       <c r="C229" t="n">
         <v>942.8900146484375</v>
@@ -6466,7 +6466,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>879.7587890625</v>
+        <v>879.7588500976562</v>
       </c>
       <c r="C230" t="n">
         <v>913.6599731445312</v>
@@ -6495,7 +6495,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>875.5835571289062</v>
+        <v>875.58349609375</v>
       </c>
       <c r="C231" t="n">
         <v>904.6199951171875</v>
@@ -6524,7 +6524,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>789.1788330078125</v>
+        <v>789.1788940429688</v>
       </c>
       <c r="C232" t="n">
         <v>815.3499755859375</v>
@@ -6582,7 +6582,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>864.9219360351562</v>
+        <v>864.921875</v>
       </c>
       <c r="C234" t="n">
         <v>888.8200073242188</v>
@@ -6611,7 +6611,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>774.0818481445312</v>
+        <v>774.0819091796875</v>
       </c>
       <c r="C235" t="n">
         <v>795.469970703125</v>
@@ -6640,7 +6640,7 @@
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>764.0587768554688</v>
+        <v>764.058837890625</v>
       </c>
       <c r="C236" t="n">
         <v>785.1699829101562</v>
